--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488154_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488154_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.0616</v>
+        <v>9.979100000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>7.7487</v>
+        <v>8.641500000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3129</v>
+        <v>1.3376</v>
       </c>
       <c r="G2" t="n">
         <v>6.3966</v>
@@ -610,13 +610,13 @@
         <v>3.3352</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.7606</v>
+        <v>-0.8431</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8282</v>
+        <v>0.06469999999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.9324</v>
+        <v>-0.9078000000000001</v>
       </c>
       <c r="V2" t="n">
         <v>2.2022</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. LÓPEZ YUSTE</t>
+          <t>J. CANDELA SOLO DE ZALDIVAR</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,58 +643,58 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3221</v>
+        <v>0.3908</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3221</v>
+        <v>-0.1274</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>0.5182</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3221</v>
+        <v>-0.5692</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3221</v>
+        <v>0.3969</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>-0.9661999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3221</v>
+        <v>-0.4855</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3221</v>
+        <v>0.0429</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>-0.5284</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>-0.0837</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>0.354</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>-0.4377</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>0.4041</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>0.3581</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>0.046</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. CANDELA SOLO DE ZALDIVAR</t>
+          <t>J. LÓPEZ YUSTE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,58 +799,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0429</v>
+        <v>0.3221</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.5738</v>
+        <v>0.3221</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6166</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.5692</v>
+        <v>0.3221</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3969</v>
+        <v>0.3221</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.9661999999999999</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.4855</v>
+        <v>0.3221</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0429</v>
+        <v>0.3221</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.5284</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0837</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0.354</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4377</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5558999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.5558999999999999</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0562</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0883</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1445</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.5463</v>
+        <v>-0.9560999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6840000000000001</v>
+        <v>-1.2169</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1377</v>
+        <v>0.2608</v>
       </c>
       <c r="G6" t="n">
         <v>-1.4513</v>
@@ -922,13 +922,13 @@
         <v>1.297</v>
       </c>
       <c r="S6" t="n">
-        <v>0.09080000000000001</v>
+        <v>-0.319</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8767</v>
+        <v>0.3439</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7859</v>
+        <v>-0.6627999999999999</v>
       </c>
       <c r="V6" t="n">
         <v>0.6289</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. NDJUNGU</t>
+          <t>G. MAIGA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8243</v>
+        <v>-1.9406</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.8957000000000001</v>
+        <v>-2.0388</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0713</v>
+        <v>0.09810000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.166</v>
+        <v>-4.2626</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.0138</v>
+        <v>-3.5822</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.1522</v>
+        <v>-0.6804</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.9599</v>
+        <v>-2.1572</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2308</v>
+        <v>-1.7224</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.1907</v>
+        <v>-0.4348</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.2061</v>
+        <v>-2.1054</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.2447</v>
+        <v>-1.8598</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0386</v>
+        <v>-0.2456</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.297</v>
+        <v>1.4823</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.891</v>
+        <v>-0.9264</v>
       </c>
       <c r="R7" t="n">
-        <v>2.594</v>
+        <v>2.4087</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7499</v>
+        <v>0.2108</v>
       </c>
       <c r="T7" t="n">
-        <v>1.4376</v>
+        <v>0.416</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6877</v>
+        <v>-0.2052</v>
       </c>
       <c r="V7" t="n">
-        <v>1.8888</v>
+        <v>0.6289</v>
       </c>
       <c r="W7" t="n">
-        <v>2.5177</v>
+        <v>0.6289</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.6289</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. MAIGA</t>
+          <t>J. NDJUNGU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.0982</v>
+        <v>-2.1478</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.3441</v>
+        <v>-1.9729</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2459</v>
+        <v>-0.1749</v>
       </c>
       <c r="G8" t="n">
-        <v>-4.2626</v>
+        <v>-2.166</v>
       </c>
       <c r="H8" t="n">
-        <v>-3.5822</v>
+        <v>-1.0138</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.6804</v>
+        <v>-1.1522</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.1572</v>
+        <v>-0.9599</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.7224</v>
+        <v>0.2308</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.4348</v>
+        <v>-1.1907</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.1054</v>
+        <v>-1.2061</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.8598</v>
+        <v>-1.2447</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2456</v>
+        <v>0.0386</v>
       </c>
       <c r="P8" t="n">
-        <v>1.4823</v>
+        <v>-1.297</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9264</v>
+        <v>-3.891</v>
       </c>
       <c r="R8" t="n">
-        <v>2.4087</v>
+        <v>2.594</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0532</v>
+        <v>-0.5736</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1107</v>
+        <v>0.3604</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0575</v>
+        <v>-0.9339</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6289</v>
+        <v>1.8888</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6289</v>
+        <v>2.5177</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.6289</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.3275</v>
+        <v>-2.3521</v>
       </c>
       <c r="E9" t="n">
         <v>-2.0039</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3235</v>
+        <v>-0.3482</v>
       </c>
       <c r="G9" t="n">
         <v>-2.6058</v>
@@ -1156,13 +1156,13 @@
         <v>0.3706</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.09229999999999999</v>
+        <v>-0.1169</v>
       </c>
       <c r="T9" t="n">
         <v>-0.0883</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.004</v>
+        <v>-0.0286</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>L. LOPEZ CALZADA</t>
+          <t>J. LOPEZ YUSTE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.0346</v>
+        <v>-3.0735</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.6453</v>
+        <v>-0.8764999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3893</v>
+        <v>-2.197</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.3433</v>
+        <v>-3.0374</v>
       </c>
       <c r="H10" t="n">
-        <v>-3.6182</v>
+        <v>-1.9649</v>
       </c>
       <c r="I10" t="n">
-        <v>1.2749</v>
+        <v>-1.0725</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.8995</v>
+        <v>-1.6543</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.2894</v>
+        <v>-0.4126</v>
       </c>
       <c r="L10" t="n">
-        <v>1.3899</v>
+        <v>-1.2416</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.4438</v>
+        <v>-1.3831</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.3288</v>
+        <v>-1.5522</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.115</v>
+        <v>0.1692</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.6676</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.9646</v>
+        <v>-1.1117</v>
       </c>
       <c r="R10" t="n">
-        <v>2.9646</v>
+        <v>2.7793</v>
       </c>
       <c r="S10" t="n">
-        <v>0.252</v>
+        <v>-0.7598</v>
       </c>
       <c r="T10" t="n">
-        <v>1.2187</v>
+        <v>0.0013</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.9668</v>
+        <v>-0.7611</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.9433</v>
+        <v>-0.9439</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.8883</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.9433</v>
+        <v>-2.8321</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.3461</v>
+        <v>-3.1443</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.1371</v>
+        <v>-2.9845</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.209</v>
+        <v>-0.1598</v>
       </c>
       <c r="G11" t="n">
         <v>-2.3431</v>
@@ -1312,13 +1312,13 @@
         <v>0.3706</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4472</v>
+        <v>-0.2453</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2736</v>
+        <v>-0.1209</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1736</v>
+        <v>-0.1244</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. LOPEZ YUSTE</t>
+          <t>L. LOPEZ CALZADA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.6042</v>
+        <v>-3.8853</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.161</v>
+        <v>-3.5699</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.4432</v>
+        <v>-0.3154</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.0374</v>
+        <v>-2.3433</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.9649</v>
+        <v>-3.6182</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.0725</v>
+        <v>1.2749</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.6543</v>
+        <v>-0.8995</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.4126</v>
+        <v>-2.2894</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.2416</v>
+        <v>1.3899</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.3831</v>
+        <v>-1.4438</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.5522</v>
+        <v>-1.3288</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1692</v>
+        <v>-0.115</v>
       </c>
       <c r="P12" t="n">
-        <v>1.6676</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1117</v>
+        <v>-2.9646</v>
       </c>
       <c r="R12" t="n">
-        <v>2.7793</v>
+        <v>2.9646</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.2906</v>
+        <v>-0.5988</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.2833</v>
+        <v>0.2941</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.0073</v>
+        <v>-0.8929</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.9439</v>
+        <v>-0.9433</v>
       </c>
       <c r="W12" t="n">
-        <v>1.8883</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.8321</v>
+        <v>-0.9433</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.032499999999999</v>
+        <v>-6.4856</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.052</v>
+        <v>-5.5051</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.9805999999999999</v>
+        <v>-0.9806000000000002</v>
       </c>
       <c r="G13" t="n">
         <v>-11.7379</v>
@@ -1459,7 +1459,7 @@
         <v>-1.3428</v>
       </c>
       <c r="P13" t="n">
-        <v>4.6322</v>
+        <v>4.632199999999999</v>
       </c>
       <c r="Q13" t="n">
         <v>-12.0435</v>
@@ -1468,10 +1468,10 @@
         <v>16.6759</v>
       </c>
       <c r="S13" t="n">
-        <v>-3.3886</v>
+        <v>-2.8416</v>
       </c>
       <c r="T13" t="n">
-        <v>1.082</v>
+        <v>1.6293</v>
       </c>
       <c r="U13" t="n">
         <v>-4.4707</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.6686</v>
+        <v>4.6488</v>
       </c>
       <c r="E14" t="n">
-        <v>1.3121</v>
+        <v>1.0184</v>
       </c>
       <c r="F14" t="n">
-        <v>4.3564</v>
+        <v>3.6305</v>
       </c>
       <c r="G14" t="n">
         <v>2.1384</v>
@@ -1546,13 +1546,13 @@
         <v>1.8529</v>
       </c>
       <c r="S14" t="n">
-        <v>3.3237</v>
+        <v>2.3039</v>
       </c>
       <c r="T14" t="n">
-        <v>1.2983</v>
+        <v>1.0045</v>
       </c>
       <c r="U14" t="n">
-        <v>2.0254</v>
+        <v>1.2994</v>
       </c>
       <c r="V14" t="n">
         <v>1.133</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. MOLINA LOPEZ</t>
+          <t>J. PINILLA NUÑEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,58 +1579,58 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.951</v>
+        <v>1.9103</v>
       </c>
       <c r="E15" t="n">
-        <v>1.4514</v>
+        <v>1.9103</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4997</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>1.2114</v>
+        <v>1.9103</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7782</v>
+        <v>1.2883</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4332</v>
+        <v>0.6221</v>
       </c>
       <c r="J15" t="n">
-        <v>1.0721</v>
+        <v>1.9103</v>
       </c>
       <c r="K15" t="n">
-        <v>1.0306</v>
+        <v>1.2883</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0415</v>
+        <v>0.6221</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1393</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2524</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>0.3917</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>0.5558999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.5558999999999999</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1838</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3793</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1955</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. PINILLA NUÑEZ</t>
+          <t>M. MOLINA LOPEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,58 +1657,58 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.9103</v>
+        <v>1.8863</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9103</v>
+        <v>1.1576</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>0.7287</v>
       </c>
       <c r="G16" t="n">
-        <v>1.9103</v>
+        <v>1.2114</v>
       </c>
       <c r="H16" t="n">
-        <v>1.2883</v>
+        <v>0.7782</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6221</v>
+        <v>0.4332</v>
       </c>
       <c r="J16" t="n">
-        <v>1.9103</v>
+        <v>1.0721</v>
       </c>
       <c r="K16" t="n">
-        <v>1.2883</v>
+        <v>1.0306</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6221</v>
+        <v>0.0415</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>0.1393</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>-0.2524</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>0.3917</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>0.1191</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>0.08550000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>0.0336</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. MOUHAMED KHALIFA</t>
+          <t>E. ANDRADE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.0259</v>
+        <v>1.8853</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1435</v>
+        <v>-0.6469</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1694</v>
+        <v>2.5322</v>
       </c>
       <c r="G17" t="n">
-        <v>1.5374</v>
+        <v>2.5567</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4973</v>
+        <v>2.7825</v>
       </c>
       <c r="I17" t="n">
-        <v>1.0401</v>
+        <v>-0.2258</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6808999999999999</v>
+        <v>1.9315</v>
       </c>
       <c r="K17" t="n">
-        <v>0.6394</v>
+        <v>1.8888</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0415</v>
+        <v>0.0427</v>
       </c>
       <c r="M17" t="n">
-        <v>0.8565</v>
+        <v>0.6252</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1421</v>
+        <v>0.8937</v>
       </c>
       <c r="O17" t="n">
-        <v>0.9986</v>
+        <v>-0.2686</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.5558999999999999</v>
+        <v>-1.6676</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.8529</v>
+        <v>-2.7793</v>
       </c>
       <c r="R17" t="n">
-        <v>1.297</v>
+        <v>1.1117</v>
       </c>
       <c r="S17" t="n">
-        <v>0.7991</v>
+        <v>0.3662</v>
       </c>
       <c r="T17" t="n">
-        <v>1.0284</v>
+        <v>0.2009</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2293</v>
+        <v>0.1654</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.7548</v>
+        <v>0.63</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.7548</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7067</v>
+        <v>1.844</v>
       </c>
       <c r="E18" t="n">
-        <v>1.8277</v>
+        <v>1.9256</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.121</v>
+        <v>-0.08160000000000001</v>
       </c>
       <c r="G18" t="n">
         <v>5.48</v>
@@ -1858,13 +1858,13 @@
         <v>1.8529</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0376</v>
+        <v>1.1748</v>
       </c>
       <c r="T18" t="n">
-        <v>0.8643</v>
+        <v>0.9622000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.8267</v>
+        <v>0.2126</v>
       </c>
       <c r="V18" t="n">
         <v>-2.958</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E. ANDRADE</t>
+          <t>D. MOUHAMED KHALIFA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6598000000000001</v>
+        <v>1.5418</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.2345</v>
+        <v>-0.3394</v>
       </c>
       <c r="F19" t="n">
-        <v>1.8943</v>
+        <v>1.8812</v>
       </c>
       <c r="G19" t="n">
-        <v>2.5567</v>
+        <v>1.5374</v>
       </c>
       <c r="H19" t="n">
-        <v>2.7825</v>
+        <v>0.4973</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2258</v>
+        <v>1.0401</v>
       </c>
       <c r="J19" t="n">
-        <v>1.9315</v>
+        <v>0.6808999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>1.8888</v>
+        <v>0.6394</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0427</v>
+        <v>0.0415</v>
       </c>
       <c r="M19" t="n">
-        <v>0.6252</v>
+        <v>0.8565</v>
       </c>
       <c r="N19" t="n">
-        <v>0.8937</v>
+        <v>-0.1421</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2686</v>
+        <v>0.9986</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.6676</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.7793</v>
+        <v>-1.8529</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1117</v>
+        <v>1.297</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8593</v>
+        <v>1.315</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3867</v>
+        <v>0.8326</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4726</v>
+        <v>0.4825</v>
       </c>
       <c r="V19" t="n">
-        <v>0.63</v>
+        <v>-0.7548</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.63</v>
+        <v>-0.7548</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. MALPICA PEREZ</t>
+          <t>R. CARRETERO GONZALEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1306</v>
+        <v>1.3992</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>2.4606</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1306</v>
+        <v>-1.0613</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1306</v>
+        <v>0.8555</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1306</v>
+        <v>-0.9233</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>1.7787</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>0.6137</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>-0.7347</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.3484</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1306</v>
+        <v>0.2418</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1306</v>
+        <v>-0.1885</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>0.4303</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>0.3706</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.297</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>0.2991</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>0.2556</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>0.0435</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.1259</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.5177</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-2.6436</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R. CARRETERO GONZALEZ</t>
+          <t>J. MALPICA PEREZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0553</v>
+        <v>0.1306</v>
       </c>
       <c r="E21" t="n">
-        <v>1.873</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.9283</v>
+        <v>0.1306</v>
       </c>
       <c r="G21" t="n">
-        <v>0.8555</v>
+        <v>0.1306</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.9233</v>
+        <v>0.1306</v>
       </c>
       <c r="I21" t="n">
-        <v>1.7787</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6137</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.7347</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>1.3484</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.2418</v>
+        <v>0.1306</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1885</v>
+        <v>0.1306</v>
       </c>
       <c r="O21" t="n">
-        <v>0.4303</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>0.3706</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.297</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.1555</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.332</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.8235</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.1259</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>2.5177</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.6436</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.5666</v>
+        <v>-0.3215</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.0123</v>
+        <v>0.1836</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.5543</v>
+        <v>-0.5051</v>
       </c>
       <c r="G22" t="n">
         <v>-0.2858</v>
@@ -2170,13 +2170,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2072</v>
+        <v>0.0379</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1094</v>
+        <v>0.0864</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0977</v>
+        <v>-0.0485</v>
       </c>
       <c r="V22" t="n">
         <v>-0.6294</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>F. GARRIDO SOTO</t>
+          <t>J. RICARDO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.9224</v>
+        <v>-0.976</v>
       </c>
       <c r="E23" t="n">
-        <v>0.4217</v>
+        <v>-2.4144</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.3441</v>
+        <v>1.4384</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.5235</v>
+        <v>-3.2534</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.2809</v>
+        <v>-0.2519</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.2427</v>
+        <v>-3.0015</v>
       </c>
       <c r="J23" t="n">
-        <v>0.09719999999999999</v>
+        <v>-3.8027</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0557</v>
+        <v>-0.6321</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0415</v>
+        <v>-3.1707</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.6207</v>
+        <v>0.5493</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.3366</v>
+        <v>0.3802</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.2841</v>
+        <v>0.1692</v>
       </c>
       <c r="P23" t="n">
-        <v>0.5558999999999999</v>
+        <v>-0.1853</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="R23" t="n">
-        <v>0.5558999999999999</v>
+        <v>1.6676</v>
       </c>
       <c r="S23" t="n">
-        <v>0.3042</v>
+        <v>1.2044</v>
       </c>
       <c r="T23" t="n">
-        <v>0.3246</v>
+        <v>1.039</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0204</v>
+        <v>0.1654</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.2589</v>
+        <v>1.2583</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>2.2022</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.2589</v>
+        <v>-0.9439</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. RICARDO</t>
+          <t>F. GARRIDO SOTO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.9278999999999999</v>
+        <v>-1.1675</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.8269</v>
+        <v>0.2259</v>
       </c>
       <c r="F24" t="n">
-        <v>0.899</v>
+        <v>-1.3933</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.2534</v>
+        <v>-0.5235</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.2519</v>
+        <v>-0.2809</v>
       </c>
       <c r="I24" t="n">
-        <v>-3.0015</v>
+        <v>-0.2427</v>
       </c>
       <c r="J24" t="n">
-        <v>-3.8027</v>
+        <v>0.09719999999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.6321</v>
+        <v>0.0557</v>
       </c>
       <c r="L24" t="n">
-        <v>-3.1707</v>
+        <v>0.0415</v>
       </c>
       <c r="M24" t="n">
-        <v>0.5493</v>
+        <v>-0.6207</v>
       </c>
       <c r="N24" t="n">
-        <v>0.3802</v>
+        <v>-0.3366</v>
       </c>
       <c r="O24" t="n">
-        <v>0.1692</v>
+        <v>-0.2841</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.1853</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.6676</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S24" t="n">
-        <v>1.2525</v>
+        <v>0.0591</v>
       </c>
       <c r="T24" t="n">
-        <v>1.6266</v>
+        <v>0.1287</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3741</v>
+        <v>-0.0696</v>
       </c>
       <c r="V24" t="n">
-        <v>1.2583</v>
+        <v>-1.2589</v>
       </c>
       <c r="W24" t="n">
-        <v>2.2022</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.9439</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.5481</v>
+        <v>-2.4845</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.5986</v>
+        <v>-4.5006</v>
       </c>
       <c r="F25" t="n">
-        <v>2.0505</v>
+        <v>2.0162</v>
       </c>
       <c r="G25" t="n">
         <v>-0.0197</v>
@@ -2404,13 +2404,13 @@
         <v>1.297</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.2903</v>
+        <v>-0.2266</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.2226</v>
+        <v>-0.1246</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.0677</v>
+        <v>-0.102</v>
       </c>
       <c r="V25" t="n">
         <v>-0.7559</v>
@@ -2437,19 +2437,19 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>7.032600000000004</v>
+        <v>10.2968</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9804000000000013</v>
+        <v>0.9806999999999997</v>
       </c>
       <c r="F26" t="n">
-        <v>6.052199999999999</v>
+        <v>9.3165</v>
       </c>
       <c r="G26" t="n">
         <v>11.7379</v>
       </c>
       <c r="H26" t="n">
-        <v>9.241300000000003</v>
+        <v>9.241300000000001</v>
       </c>
       <c r="I26" t="n">
         <v>2.4966</v>
@@ -2458,10 +2458,10 @@
         <v>7.522500000000002</v>
       </c>
       <c r="K26" t="n">
-        <v>6.179599999999999</v>
+        <v>6.1796</v>
       </c>
       <c r="L26" t="n">
-        <v>1.3429</v>
+        <v>1.342900000000001</v>
       </c>
       <c r="M26" t="n">
         <v>4.2154</v>
@@ -2482,13 +2482,13 @@
         <v>12.0438</v>
       </c>
       <c r="S26" t="n">
-        <v>3.388600000000001</v>
+        <v>6.652899999999999</v>
       </c>
       <c r="T26" t="n">
         <v>4.4708</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.082100000000001</v>
+        <v>2.1823</v>
       </c>
       <c r="V26" t="n">
         <v>-3.4616</v>
